--- a/2_elektrik_enerjisinin_kaynaklara_gore kurulu_gucu_ve_uretimi.xlsx
+++ b/2_elektrik_enerjisinin_kaynaklara_gore kurulu_gucu_ve_uretimi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\volkan.ediger\OneDrive - Kadir Has University\Masaüstü\İstemi 9 Haz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/istemiberk/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E0BDD3-35EF-4E8A-9821-8497B97D7806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1B4264-E12D-1244-9FDC-B1BA4CE58371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{E3C94023-D689-4148-BE44-0A846AFF29B7}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17180" xr2:uid="{E3C94023-D689-4148-BE44-0A846AFF29B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Kurulu Güç" sheetId="14" r:id="rId1"/>
@@ -100,7 +100,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,30 +590,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1C5AF0-0992-9747-81B8-107990B81481}">
-  <dimension ref="A1:S104"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="13"/>
+  <dimension ref="A1:W104"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.36328125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="6.90625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.81640625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="7.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="6.90625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.6328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="10.81640625" style="4"/>
+    <col min="12" max="12" width="8.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.83203125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="7.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="6.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="9" customFormat="1" ht="39">
+    <row r="1" spans="1:23" s="9" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>13</v>
       </c>
@@ -670,7 +670,7 @@
       </c>
       <c r="S1" s="8"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>1923</v>
       </c>
@@ -727,8 +727,12 @@
         <v>29.8</v>
       </c>
       <c r="S2" s="11"/>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>1924</v>
       </c>
@@ -785,8 +789,12 @@
         <v>29.833000000000006</v>
       </c>
       <c r="S3" s="11"/>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>1925</v>
       </c>
@@ -843,8 +851,12 @@
         <v>30.956999999999997</v>
       </c>
       <c r="S4" s="11"/>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <v>1926</v>
       </c>
@@ -901,8 +913,12 @@
         <v>50.19400000000001</v>
       </c>
       <c r="S5" s="11"/>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>1927</v>
       </c>
@@ -959,8 +975,12 @@
         <v>51.913000000000011</v>
       </c>
       <c r="S6" s="11"/>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>1928</v>
       </c>
@@ -1017,8 +1037,12 @@
         <v>63.442999999999998</v>
       </c>
       <c r="S7" s="11"/>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>1929</v>
       </c>
@@ -1075,8 +1099,12 @@
         <v>68.024000000000001</v>
       </c>
       <c r="S8" s="11"/>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <v>1930</v>
       </c>
@@ -1133,8 +1161,12 @@
         <v>74.635999999999996</v>
       </c>
       <c r="S9" s="11"/>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>1931</v>
       </c>
@@ -1191,8 +1223,12 @@
         <v>98.291000000000011</v>
       </c>
       <c r="S10" s="11"/>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>1932</v>
       </c>
@@ -1249,8 +1285,12 @@
         <v>100.262</v>
       </c>
       <c r="S11" s="11"/>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>1933</v>
       </c>
@@ -1307,8 +1347,12 @@
         <v>103.99400000000001</v>
       </c>
       <c r="S12" s="11"/>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>1934</v>
       </c>
@@ -1365,8 +1409,12 @@
         <v>112.51400000000001</v>
       </c>
       <c r="S13" s="11"/>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>1935</v>
       </c>
@@ -1423,8 +1471,12 @@
         <v>119.16</v>
       </c>
       <c r="S14" s="11"/>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>1936</v>
       </c>
@@ -1481,8 +1533,12 @@
         <v>136.76</v>
       </c>
       <c r="S15" s="11"/>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>1937</v>
       </c>
@@ -1539,8 +1595,12 @@
         <v>155.43100000000001</v>
       </c>
       <c r="S16" s="11"/>
-    </row>
-    <row r="17" spans="1:19">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
         <v>1938</v>
       </c>
@@ -1597,8 +1657,12 @@
         <v>163.59100000000001</v>
       </c>
       <c r="S17" s="11"/>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
         <v>1939</v>
       </c>
@@ -1655,8 +1719,12 @@
         <v>202.51800000000003</v>
       </c>
       <c r="S18" s="11"/>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <v>1940</v>
       </c>
@@ -1713,8 +1781,12 @@
         <v>217</v>
       </c>
       <c r="S19" s="11"/>
-    </row>
-    <row r="20" spans="1:19">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
         <v>1941</v>
       </c>
@@ -1771,8 +1843,12 @@
         <v>222</v>
       </c>
       <c r="S20" s="11"/>
-    </row>
-    <row r="21" spans="1:19">
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="10">
         <v>1942</v>
       </c>
@@ -1829,8 +1905,12 @@
         <v>226.7</v>
       </c>
       <c r="S21" s="11"/>
-    </row>
-    <row r="22" spans="1:19">
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>1943</v>
       </c>
@@ -1887,8 +1967,12 @@
         <v>236.4</v>
       </c>
       <c r="S22" s="11"/>
-    </row>
-    <row r="23" spans="1:19">
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <v>1944</v>
       </c>
@@ -1945,8 +2029,12 @@
         <v>243.9</v>
       </c>
       <c r="S23" s="11"/>
-    </row>
-    <row r="24" spans="1:19">
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="10">
         <v>1945</v>
       </c>
@@ -2003,8 +2091,12 @@
         <v>246.1</v>
       </c>
       <c r="S24" s="11"/>
-    </row>
-    <row r="25" spans="1:19">
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="10">
         <v>1946</v>
       </c>
@@ -2061,8 +2153,12 @@
         <v>247.4</v>
       </c>
       <c r="S25" s="11"/>
-    </row>
-    <row r="26" spans="1:19">
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>1947</v>
       </c>
@@ -2119,8 +2215,12 @@
         <v>251.4</v>
       </c>
       <c r="S26" s="11"/>
-    </row>
-    <row r="27" spans="1:19">
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>1948</v>
       </c>
@@ -2177,8 +2277,12 @@
         <v>305.5</v>
       </c>
       <c r="S27" s="11"/>
-    </row>
-    <row r="28" spans="1:19">
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>1949</v>
       </c>
@@ -2235,8 +2339,12 @@
         <v>381.8</v>
       </c>
       <c r="S28" s="11"/>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>1950</v>
       </c>
@@ -2293,8 +2401,12 @@
         <v>407.8</v>
       </c>
       <c r="S29" s="11"/>
-    </row>
-    <row r="30" spans="1:19">
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>1951</v>
       </c>
@@ -2351,8 +2463,12 @@
         <v>423.2</v>
       </c>
       <c r="S30" s="11"/>
-    </row>
-    <row r="31" spans="1:19">
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>1952</v>
       </c>
@@ -2409,8 +2525,12 @@
         <v>437.8</v>
       </c>
       <c r="S31" s="11"/>
-    </row>
-    <row r="32" spans="1:19">
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>1953</v>
       </c>
@@ -2467,8 +2587,12 @@
         <v>499.5</v>
       </c>
       <c r="S32" s="11"/>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>1954</v>
       </c>
@@ -2525,8 +2649,12 @@
         <v>516.9</v>
       </c>
       <c r="S33" s="11"/>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>1955</v>
       </c>
@@ -2583,8 +2711,12 @@
         <v>611.6</v>
       </c>
       <c r="S34" s="11"/>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>1956</v>
       </c>
@@ -2641,8 +2773,12 @@
         <v>886.1</v>
       </c>
       <c r="S35" s="11"/>
-    </row>
-    <row r="36" spans="1:19">
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>1957</v>
       </c>
@@ -2699,8 +2835,12 @@
         <v>939.4</v>
       </c>
       <c r="S36" s="11"/>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>1958</v>
       </c>
@@ -2757,8 +2897,12 @@
         <v>1030</v>
       </c>
       <c r="S37" s="11"/>
-    </row>
-    <row r="38" spans="1:19">
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>1959</v>
       </c>
@@ -2815,8 +2959,12 @@
         <v>1161</v>
       </c>
       <c r="S38" s="11"/>
-    </row>
-    <row r="39" spans="1:19">
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>1960</v>
       </c>
@@ -2873,8 +3021,12 @@
         <v>1272.4000000000001</v>
       </c>
       <c r="S39" s="11"/>
-    </row>
-    <row r="40" spans="1:19">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>1961</v>
       </c>
@@ -2931,8 +3083,12 @@
         <v>1323.9</v>
       </c>
       <c r="S40" s="11"/>
-    </row>
-    <row r="41" spans="1:19">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>1962</v>
       </c>
@@ -2989,8 +3145,12 @@
         <v>1370.8</v>
       </c>
       <c r="S41" s="11"/>
-    </row>
-    <row r="42" spans="1:19">
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>1963</v>
       </c>
@@ -3047,8 +3207,12 @@
         <v>1381.1</v>
       </c>
       <c r="S42" s="11"/>
-    </row>
-    <row r="43" spans="1:19">
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>1964</v>
       </c>
@@ -3105,8 +3269,12 @@
         <v>1418.3</v>
       </c>
       <c r="S43" s="11"/>
-    </row>
-    <row r="44" spans="1:19">
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>1965</v>
       </c>
@@ -3163,8 +3331,12 @@
         <v>1490.5</v>
       </c>
       <c r="S44" s="11"/>
-    </row>
-    <row r="45" spans="1:19">
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>1966</v>
       </c>
@@ -3221,8 +3393,12 @@
         <v>1644.3</v>
       </c>
       <c r="S45" s="11"/>
-    </row>
-    <row r="46" spans="1:19">
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>1967</v>
       </c>
@@ -3279,8 +3455,12 @@
         <v>1962.2</v>
       </c>
       <c r="S46" s="11"/>
-    </row>
-    <row r="47" spans="1:19">
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>1968</v>
       </c>
@@ -3337,8 +3517,12 @@
         <v>1966.6</v>
       </c>
       <c r="S47" s="11"/>
-    </row>
-    <row r="48" spans="1:19">
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="3"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>1969</v>
       </c>
@@ -3395,8 +3579,12 @@
         <v>1967.2</v>
       </c>
       <c r="S48" s="11"/>
-    </row>
-    <row r="49" spans="1:19">
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>1970</v>
       </c>
@@ -3453,8 +3641,12 @@
         <v>2234.9</v>
       </c>
       <c r="S49" s="11"/>
-    </row>
-    <row r="50" spans="1:19">
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>1971</v>
       </c>
@@ -3511,8 +3703,12 @@
         <v>2577.9</v>
       </c>
       <c r="S50" s="11"/>
-    </row>
-    <row r="51" spans="1:19">
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>1972</v>
       </c>
@@ -3568,8 +3764,12 @@
         <v>2711.3</v>
       </c>
       <c r="S51" s="11"/>
-    </row>
-    <row r="52" spans="1:19">
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>1973</v>
       </c>
@@ -3625,8 +3825,12 @@
         <v>3192.5</v>
       </c>
       <c r="S52" s="11"/>
-    </row>
-    <row r="53" spans="1:19">
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>1974</v>
       </c>
@@ -3682,8 +3886,12 @@
         <v>3732.1</v>
       </c>
       <c r="S53" s="11"/>
-    </row>
-    <row r="54" spans="1:19">
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54" s="10">
         <v>1975</v>
       </c>
@@ -3739,8 +3947,12 @@
         <v>4186.6000000000004</v>
       </c>
       <c r="S54" s="11"/>
-    </row>
-    <row r="55" spans="1:19">
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55" s="10">
         <v>1976</v>
       </c>
@@ -3796,8 +4008,12 @@
         <v>4364.2</v>
       </c>
       <c r="S55" s="11"/>
-    </row>
-    <row r="56" spans="1:19">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56" s="10">
         <v>1977</v>
       </c>
@@ -3853,8 +4069,12 @@
         <v>4727.2</v>
       </c>
       <c r="S56" s="11"/>
-    </row>
-    <row r="57" spans="1:19">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57" s="10">
         <v>1978</v>
       </c>
@@ -3910,8 +4130,12 @@
         <v>4868.7</v>
       </c>
       <c r="S57" s="11"/>
-    </row>
-    <row r="58" spans="1:19">
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58" s="10">
         <v>1979</v>
       </c>
@@ -3967,8 +4191,12 @@
         <v>5118.7</v>
       </c>
       <c r="S58" s="11"/>
-    </row>
-    <row r="59" spans="1:19">
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59" s="10">
         <v>1980</v>
       </c>
@@ -4024,8 +4252,12 @@
         <v>5118.7</v>
       </c>
       <c r="S59" s="11"/>
-    </row>
-    <row r="60" spans="1:19">
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60" s="10">
         <v>1981</v>
       </c>
@@ -4081,8 +4313,12 @@
         <v>5537.6</v>
       </c>
       <c r="S60" s="11"/>
-    </row>
-    <row r="61" spans="1:19">
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61" s="10">
         <v>1982</v>
       </c>
@@ -4138,8 +4374,12 @@
         <v>6638.6</v>
       </c>
       <c r="S61" s="11"/>
-    </row>
-    <row r="62" spans="1:19">
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62" s="10">
         <v>1983</v>
       </c>
@@ -4195,8 +4435,12 @@
         <v>6935.1</v>
       </c>
       <c r="S62" s="11"/>
-    </row>
-    <row r="63" spans="1:19">
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63" s="10">
         <v>1984</v>
       </c>
@@ -4252,8 +4496,12 @@
         <v>8461.6</v>
       </c>
       <c r="S63" s="11"/>
-    </row>
-    <row r="64" spans="1:19">
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64" s="10">
         <v>1985</v>
       </c>
@@ -4309,8 +4557,12 @@
         <v>9121.6</v>
       </c>
       <c r="S64" s="11"/>
-    </row>
-    <row r="65" spans="1:19">
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65" s="10">
         <v>1986</v>
       </c>
@@ -4366,8 +4618,12 @@
         <v>10115.200000000001</v>
       </c>
       <c r="S65" s="11"/>
-    </row>
-    <row r="66" spans="1:19">
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66" s="10">
         <v>1987</v>
       </c>
@@ -4423,8 +4679,12 @@
         <v>12495.1</v>
       </c>
       <c r="S66" s="11"/>
-    </row>
-    <row r="67" spans="1:19">
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67" s="10">
         <v>1988</v>
       </c>
@@ -4480,8 +4740,12 @@
         <v>14520.599999999999</v>
       </c>
       <c r="S67" s="11"/>
-    </row>
-    <row r="68" spans="1:19">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68" s="10">
         <v>1989</v>
       </c>
@@ -4537,8 +4801,12 @@
         <v>15808.2</v>
       </c>
       <c r="S68" s="11"/>
-    </row>
-    <row r="69" spans="1:19">
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69" s="10">
         <v>1990</v>
       </c>
@@ -4594,8 +4862,12 @@
         <v>16317.599999999999</v>
       </c>
       <c r="S69" s="11"/>
-    </row>
-    <row r="70" spans="1:19">
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70" s="10">
         <v>1991</v>
       </c>
@@ -4650,8 +4922,12 @@
       <c r="R70" s="1">
         <v>17209.099999999999</v>
       </c>
-    </row>
-    <row r="71" spans="1:19">
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71" s="10">
         <v>1992</v>
       </c>
@@ -4707,8 +4983,12 @@
         <v>18716.099999999999</v>
       </c>
       <c r="S71" s="11"/>
-    </row>
-    <row r="72" spans="1:19">
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
+      <c r="W71" s="3"/>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72" s="10">
         <v>1993</v>
       </c>
@@ -4764,8 +5044,12 @@
         <v>20337.599999999999</v>
       </c>
       <c r="S72" s="12"/>
-    </row>
-    <row r="73" spans="1:19">
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73" s="10">
         <v>1994</v>
       </c>
@@ -4821,8 +5105,12 @@
         <v>20859.800000000003</v>
       </c>
       <c r="S73" s="3"/>
-    </row>
-    <row r="74" spans="1:19">
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74" s="10">
         <v>1995</v>
       </c>
@@ -4878,8 +5166,12 @@
         <v>20954.3</v>
       </c>
       <c r="S74" s="11"/>
-    </row>
-    <row r="75" spans="1:19">
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75" s="10">
         <v>1996</v>
       </c>
@@ -4935,8 +5227,12 @@
         <v>21249.4</v>
       </c>
       <c r="S75" s="11"/>
-    </row>
-    <row r="76" spans="1:19">
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76" s="10">
         <v>1997</v>
       </c>
@@ -4992,8 +5288,12 @@
         <v>21891.9</v>
       </c>
       <c r="S76" s="12"/>
-    </row>
-    <row r="77" spans="1:19">
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77" s="10">
         <v>1998</v>
       </c>
@@ -5049,8 +5349,12 @@
         <v>23354</v>
       </c>
       <c r="S77" s="11"/>
-    </row>
-    <row r="78" spans="1:19">
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78" s="10">
         <v>1999</v>
       </c>
@@ -5106,8 +5410,12 @@
         <v>26119.300000000003</v>
       </c>
       <c r="S78" s="11"/>
-    </row>
-    <row r="79" spans="1:19">
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79" s="10">
         <v>2000</v>
       </c>
@@ -5163,8 +5471,12 @@
         <v>27264.1</v>
       </c>
       <c r="S79" s="11"/>
-    </row>
-    <row r="80" spans="1:19">
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79" s="3"/>
+      <c r="W79" s="3"/>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80" s="10">
         <v>2001</v>
       </c>
@@ -5220,8 +5532,12 @@
         <v>28332.399999999998</v>
       </c>
       <c r="S80" s="11"/>
-    </row>
-    <row r="81" spans="1:19">
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81" s="10">
         <v>2002</v>
       </c>
@@ -5277,8 +5593,12 @@
         <v>31845.8</v>
       </c>
       <c r="S81" s="11"/>
-    </row>
-    <row r="82" spans="1:19">
+      <c r="T81" s="3"/>
+      <c r="U81" s="3"/>
+      <c r="V81" s="3"/>
+      <c r="W81" s="3"/>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82" s="10">
         <v>2003</v>
       </c>
@@ -5334,8 +5654,12 @@
         <v>35587</v>
       </c>
       <c r="S82" s="11"/>
-    </row>
-    <row r="83" spans="1:19">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83" s="10">
         <v>2004</v>
       </c>
@@ -5391,8 +5715,12 @@
         <v>36824</v>
       </c>
       <c r="S83" s="11"/>
-    </row>
-    <row r="84" spans="1:19">
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84" s="10">
         <v>2005</v>
       </c>
@@ -5448,8 +5776,12 @@
         <v>38843.5</v>
       </c>
       <c r="S84" s="11"/>
-    </row>
-    <row r="85" spans="1:19">
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85" s="10">
         <v>2006</v>
       </c>
@@ -5505,8 +5837,12 @@
         <v>40564.800000000003</v>
       </c>
       <c r="S85" s="11"/>
-    </row>
-    <row r="86" spans="1:19">
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86" s="10">
         <v>2007</v>
       </c>
@@ -5562,8 +5898,12 @@
         <v>40835.699999999997</v>
       </c>
       <c r="S86" s="11"/>
-    </row>
-    <row r="87" spans="1:19">
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87" s="10">
         <v>2008</v>
       </c>
@@ -5619,8 +5959,12 @@
         <v>41817.197</v>
       </c>
       <c r="S87" s="11"/>
-    </row>
-    <row r="88" spans="1:19">
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A88" s="10">
         <v>2009</v>
       </c>
@@ -5676,8 +6020,12 @@
         <v>44761.171999999999</v>
       </c>
       <c r="S88" s="11"/>
-    </row>
-    <row r="89" spans="1:19">
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A89" s="10">
         <v>2010</v>
       </c>
@@ -5733,8 +6081,12 @@
         <v>49524.099999999991</v>
       </c>
       <c r="S89" s="11"/>
-    </row>
-    <row r="90" spans="1:19">
+      <c r="T89" s="3"/>
+      <c r="U89" s="3"/>
+      <c r="V89" s="3"/>
+      <c r="W89" s="3"/>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90" s="10">
         <v>2011</v>
       </c>
@@ -5790,8 +6142,12 @@
         <v>52911.099999999991</v>
       </c>
       <c r="S90" s="11"/>
-    </row>
-    <row r="91" spans="1:19">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91" s="10">
         <v>2012</v>
       </c>
@@ -5847,8 +6203,12 @@
         <v>57059.406999999992</v>
       </c>
       <c r="S91" s="11"/>
-    </row>
-    <row r="92" spans="1:19">
+      <c r="T91" s="3"/>
+      <c r="U91" s="3"/>
+      <c r="V91" s="3"/>
+      <c r="W91" s="3"/>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92" s="10">
         <v>2013</v>
       </c>
@@ -5904,8 +6264,12 @@
         <v>64007.5</v>
       </c>
       <c r="S92" s="11"/>
-    </row>
-    <row r="93" spans="1:19">
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A93" s="10">
         <v>2014</v>
       </c>
@@ -5961,8 +6325,12 @@
         <v>69519.76999999999</v>
       </c>
       <c r="S93" s="11"/>
-    </row>
-    <row r="94" spans="1:19">
+      <c r="T93" s="3"/>
+      <c r="U93" s="3"/>
+      <c r="V93" s="3"/>
+      <c r="W93" s="3"/>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A94" s="10">
         <v>2015</v>
       </c>
@@ -6018,8 +6386,12 @@
         <v>73146.740600000005</v>
       </c>
       <c r="S94" s="11"/>
-    </row>
-    <row r="95" spans="1:19">
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A95" s="10">
         <v>2016</v>
       </c>
@@ -6075,8 +6447,12 @@
         <v>78497.381640000007</v>
       </c>
       <c r="S95" s="11"/>
-    </row>
-    <row r="96" spans="1:19">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A96" s="10">
         <v>2017</v>
       </c>
@@ -6132,8 +6508,12 @@
         <v>85200.031999999992</v>
       </c>
       <c r="S96" s="11"/>
-    </row>
-    <row r="97" spans="1:19">
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <v>2018</v>
       </c>
@@ -6189,8 +6569,12 @@
         <v>88550.779137878781</v>
       </c>
       <c r="S97" s="11"/>
-    </row>
-    <row r="98" spans="1:19">
+      <c r="T97" s="3"/>
+      <c r="U97" s="3"/>
+      <c r="V97" s="3"/>
+      <c r="W97" s="3"/>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98" s="10">
         <v>2019</v>
       </c>
@@ -6246,8 +6630,12 @@
         <v>91266.991543917655</v>
       </c>
       <c r="S98" s="11"/>
-    </row>
-    <row r="99" spans="1:19">
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99" s="10">
         <v>2020</v>
       </c>
@@ -6303,8 +6691,12 @@
         <v>95890.607055</v>
       </c>
       <c r="S99" s="11"/>
-    </row>
-    <row r="100" spans="1:19">
+      <c r="T99" s="3"/>
+      <c r="U99" s="3"/>
+      <c r="V99" s="3"/>
+      <c r="W99" s="3"/>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100" s="10">
         <v>2021</v>
       </c>
@@ -6360,8 +6752,12 @@
         <v>99819.612829999984</v>
       </c>
       <c r="S100" s="11"/>
-    </row>
-    <row r="101" spans="1:19">
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101" s="10">
         <v>2022</v>
       </c>
@@ -6417,8 +6813,12 @@
         <v>103809.25900000001</v>
       </c>
       <c r="S101" s="11"/>
-    </row>
-    <row r="102" spans="1:19">
+      <c r="T101" s="3"/>
+      <c r="U101" s="3"/>
+      <c r="V101" s="3"/>
+      <c r="W101" s="3"/>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102" s="10">
         <v>2023</v>
       </c>
@@ -6474,8 +6874,12 @@
         <v>110913.976729</v>
       </c>
       <c r="S102" s="11"/>
-    </row>
-    <row r="104" spans="1:19">
+      <c r="T102" s="3"/>
+      <c r="U102" s="3"/>
+      <c r="V102" s="3"/>
+      <c r="W102" s="3"/>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J104" s="3"/>
     </row>
   </sheetData>
@@ -6485,30 +6889,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A463FD1-3795-4045-8E78-2CA146430041}">
-  <dimension ref="A1:R105"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="13"/>
+  <dimension ref="A1:W105"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7265625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="11.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="6.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.6328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="10.81640625" style="4"/>
+    <col min="15" max="16" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="5" customFormat="1" ht="25.5" customHeight="1">
+    <row r="1" spans="1:23" s="5" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>13</v>
       </c>
@@ -6563,8 +6967,12 @@
       <c r="R1" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>1923</v>
       </c>
@@ -6619,8 +7027,12 @@
       <c r="R2" s="1">
         <v>44.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>1924</v>
       </c>
@@ -6675,8 +7087,12 @@
       <c r="R3" s="1">
         <v>44.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>1925</v>
       </c>
@@ -6731,8 +7147,12 @@
       <c r="R4" s="1">
         <v>45.300000000000004</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <v>1926</v>
       </c>
@@ -6787,8 +7207,12 @@
       <c r="R5" s="1">
         <v>65.8</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>1927</v>
       </c>
@@ -6843,8 +7267,12 @@
       <c r="R6" s="1">
         <v>70.100000000000009</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>1928</v>
       </c>
@@ -6899,8 +7327,12 @@
       <c r="R7" s="1">
         <v>89.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>1929</v>
       </c>
@@ -6955,8 +7387,12 @@
       <c r="R8" s="1">
         <v>97.8</v>
       </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <v>1930</v>
       </c>
@@ -7011,8 +7447,12 @@
       <c r="R9" s="1">
         <v>106.30000000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>1931</v>
       </c>
@@ -7067,8 +7507,12 @@
       <c r="R10" s="1">
         <v>117.9</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>1932</v>
       </c>
@@ -7123,8 +7567,12 @@
       <c r="R11" s="1">
         <v>131.6</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>1933</v>
       </c>
@@ -7179,8 +7627,12 @@
       <c r="R12" s="1">
         <v>151.9</v>
       </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>1934</v>
       </c>
@@ -7235,8 +7687,12 @@
       <c r="R13" s="1">
         <v>195.2</v>
       </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>1935</v>
       </c>
@@ -7291,8 +7747,12 @@
       <c r="R14" s="1">
         <v>212.9</v>
       </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>1936</v>
       </c>
@@ -7347,8 +7807,12 @@
       <c r="R15" s="1">
         <v>231.1</v>
       </c>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>1937</v>
       </c>
@@ -7403,8 +7867,12 @@
       <c r="R16" s="1">
         <v>289.8</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
         <v>1938</v>
       </c>
@@ -7459,8 +7927,12 @@
       <c r="R17" s="1">
         <v>312.10000000000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
         <v>1939</v>
       </c>
@@ -7515,8 +7987,12 @@
       <c r="R18" s="1">
         <v>353.3</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <v>1940</v>
       </c>
@@ -7571,8 +8047,12 @@
       <c r="R19" s="1">
         <v>396.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
         <v>1941</v>
       </c>
@@ -7627,8 +8107,12 @@
       <c r="R20" s="1">
         <v>415.2</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="10">
         <v>1942</v>
       </c>
@@ -7683,8 +8167,12 @@
       <c r="R21" s="1">
         <v>408.2</v>
       </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>1943</v>
       </c>
@@ -7739,8 +8227,12 @@
       <c r="R22" s="1">
         <v>457.40000000000003</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <v>1944</v>
       </c>
@@ -7795,8 +8287,12 @@
       <c r="R23" s="1">
         <v>496.1</v>
       </c>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="10">
         <v>1945</v>
       </c>
@@ -7851,8 +8347,12 @@
       <c r="R24" s="1">
         <v>527.79999999999995</v>
       </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="10">
         <v>1946</v>
       </c>
@@ -7907,8 +8407,12 @@
       <c r="R25" s="1">
         <v>562.6</v>
       </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>1947</v>
       </c>
@@ -7963,8 +8467,12 @@
       <c r="R26" s="1">
         <v>625.00000000000011</v>
       </c>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>1948</v>
       </c>
@@ -8019,8 +8527,12 @@
       <c r="R27" s="1">
         <v>676.3</v>
       </c>
-    </row>
-    <row r="28" spans="1:18">
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>1949</v>
       </c>
@@ -8075,8 +8587,12 @@
       <c r="R28" s="1">
         <v>736.59999999999991</v>
       </c>
-    </row>
-    <row r="29" spans="1:18">
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>1950</v>
       </c>
@@ -8131,8 +8647,12 @@
       <c r="R29" s="1">
         <v>789.5</v>
       </c>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>1951</v>
       </c>
@@ -8187,8 +8707,12 @@
       <c r="R30" s="1">
         <v>887.90000000000009</v>
       </c>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>1952</v>
       </c>
@@ -8243,8 +8767,12 @@
       <c r="R31" s="1">
         <v>1020.1999999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>1953</v>
       </c>
@@ -8299,8 +8827,12 @@
       <c r="R32" s="1">
         <v>1200.8</v>
       </c>
-    </row>
-    <row r="33" spans="1:18">
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>1954</v>
       </c>
@@ -8355,8 +8887,12 @@
       <c r="R33" s="1">
         <v>1402.5</v>
       </c>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>1955</v>
       </c>
@@ -8411,8 +8947,12 @@
       <c r="R34" s="1">
         <v>1579.8</v>
       </c>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>1956</v>
       </c>
@@ -8467,8 +9007,12 @@
       <c r="R35" s="1">
         <v>1819.1000000000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>1957</v>
       </c>
@@ -8523,8 +9067,12 @@
       <c r="R36" s="1">
         <v>2056.6</v>
       </c>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>1958</v>
       </c>
@@ -8579,8 +9127,12 @@
       <c r="R37" s="1">
         <v>2303.3999999999996</v>
       </c>
-    </row>
-    <row r="38" spans="1:18">
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>1959</v>
       </c>
@@ -8635,8 +9187,12 @@
       <c r="R38" s="1">
         <v>2587.3000000000002</v>
       </c>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>1960</v>
       </c>
@@ -8691,8 +9247,12 @@
       <c r="R39" s="1">
         <v>2815.1</v>
       </c>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>1961</v>
       </c>
@@ -8747,8 +9307,12 @@
       <c r="R40" s="1">
         <v>3011.1000000000004</v>
       </c>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>1962</v>
       </c>
@@ -8803,8 +9367,12 @@
       <c r="R41" s="1">
         <v>3559.6000000000004</v>
       </c>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>1963</v>
       </c>
@@ -8859,8 +9427,12 @@
       <c r="R42" s="1">
         <v>3983.4</v>
       </c>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>1964</v>
       </c>
@@ -8915,8 +9487,12 @@
       <c r="R43" s="1">
         <v>4450.8999999999996</v>
       </c>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>1965</v>
       </c>
@@ -8971,8 +9547,12 @@
       <c r="R44" s="1">
         <v>4952.7</v>
       </c>
-    </row>
-    <row r="45" spans="1:18">
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>1966</v>
       </c>
@@ -9027,8 +9607,12 @@
       <c r="R45" s="1">
         <v>5550.9</v>
       </c>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>1967</v>
       </c>
@@ -9083,8 +9667,12 @@
       <c r="R46" s="1">
         <v>6211.8000000000011</v>
       </c>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>1968</v>
       </c>
@@ -9139,8 +9727,12 @@
       <c r="R47" s="1">
         <v>6935.8</v>
       </c>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="3"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>1969</v>
       </c>
@@ -9195,8 +9787,12 @@
       <c r="R48" s="1">
         <v>7838</v>
       </c>
-    </row>
-    <row r="49" spans="1:18">
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>1970</v>
       </c>
@@ -9251,8 +9847,12 @@
       <c r="R49" s="1">
         <v>8623</v>
       </c>
-    </row>
-    <row r="50" spans="1:18">
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>1971</v>
       </c>
@@ -9307,8 +9907,12 @@
       <c r="R50" s="1">
         <v>9781.0999999999985</v>
       </c>
-    </row>
-    <row r="51" spans="1:18">
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>1972</v>
       </c>
@@ -9364,8 +9968,12 @@
       <c r="R51" s="1">
         <v>11241.9</v>
       </c>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>1973</v>
       </c>
@@ -9421,8 +10029,12 @@
       <c r="R52" s="1">
         <v>12425.199999999999</v>
       </c>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>1974</v>
       </c>
@@ -9478,8 +10090,12 @@
       <c r="R53" s="1">
         <v>13477</v>
       </c>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54" s="10">
         <v>1975</v>
       </c>
@@ -9535,8 +10151,12 @@
       <c r="R54" s="1">
         <v>15622.800000000001</v>
       </c>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55" s="10">
         <v>1976</v>
       </c>
@@ -9592,8 +10212,12 @@
       <c r="R55" s="1">
         <v>18282.8</v>
       </c>
-    </row>
-    <row r="56" spans="1:18">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56" s="10">
         <v>1977</v>
       </c>
@@ -9649,8 +10273,12 @@
       <c r="R56" s="1">
         <v>20564.599999999999</v>
       </c>
-    </row>
-    <row r="57" spans="1:18">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57" s="10">
         <v>1978</v>
       </c>
@@ -9706,8 +10334,12 @@
       <c r="R57" s="1">
         <v>21726.1</v>
       </c>
-    </row>
-    <row r="58" spans="1:18">
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58" s="10">
         <v>1979</v>
       </c>
@@ -9763,8 +10395,12 @@
       <c r="R58" s="1">
         <v>22521.9</v>
       </c>
-    </row>
-    <row r="59" spans="1:18">
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59" s="10">
         <v>1980</v>
       </c>
@@ -9820,8 +10456,12 @@
       <c r="R59" s="1">
         <v>23275.4</v>
       </c>
-    </row>
-    <row r="60" spans="1:18">
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60" s="10">
         <v>1981</v>
       </c>
@@ -9877,8 +10517,12 @@
       <c r="R60" s="1">
         <v>24672.800000000003</v>
       </c>
-    </row>
-    <row r="61" spans="1:18">
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61" s="10">
         <v>1982</v>
       </c>
@@ -9934,8 +10578,12 @@
       <c r="R61" s="1">
         <v>26551.5</v>
       </c>
-    </row>
-    <row r="62" spans="1:18">
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62" s="10">
         <v>1983</v>
       </c>
@@ -9991,8 +10639,12 @@
       <c r="R62" s="1">
         <v>27346.799999999999</v>
       </c>
-    </row>
-    <row r="63" spans="1:18">
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63" s="10">
         <v>1984</v>
       </c>
@@ -10048,8 +10700,12 @@
       <c r="R63" s="1">
         <v>30613.5</v>
       </c>
-    </row>
-    <row r="64" spans="1:18">
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64" s="10">
         <v>1985</v>
       </c>
@@ -10105,8 +10761,12 @@
       <c r="R64" s="1">
         <v>34218.9</v>
       </c>
-    </row>
-    <row r="65" spans="1:18">
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65" s="10">
         <v>1986</v>
       </c>
@@ -10162,8 +10822,12 @@
       <c r="R65" s="1">
         <v>39694.800000000003</v>
       </c>
-    </row>
-    <row r="66" spans="1:18">
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66" s="10">
         <v>1987</v>
       </c>
@@ -10219,8 +10883,12 @@
       <c r="R66" s="1">
         <v>44352.9</v>
       </c>
-    </row>
-    <row r="67" spans="1:18">
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67" s="10">
         <v>1988</v>
       </c>
@@ -10276,8 +10944,12 @@
       <c r="R67" s="1">
         <v>48048.799999999996</v>
       </c>
-    </row>
-    <row r="68" spans="1:18">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68" s="10">
         <v>1989</v>
       </c>
@@ -10333,8 +11005,12 @@
       <c r="R68" s="1">
         <v>52043.199999999997</v>
       </c>
-    </row>
-    <row r="69" spans="1:18">
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69" s="10">
         <v>1990</v>
       </c>
@@ -10390,8 +11066,12 @@
       <c r="R69" s="1">
         <v>57543</v>
       </c>
-    </row>
-    <row r="70" spans="1:18">
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70" s="10">
         <v>1991</v>
       </c>
@@ -10447,8 +11127,12 @@
       <c r="R70" s="1">
         <v>60246.3</v>
       </c>
-    </row>
-    <row r="71" spans="1:18">
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71" s="10">
         <v>1992</v>
       </c>
@@ -10504,8 +11188,12 @@
       <c r="R71" s="1">
         <v>67342.200000000012</v>
       </c>
-    </row>
-    <row r="72" spans="1:18">
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
+      <c r="W71" s="3"/>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72" s="10">
         <v>1993</v>
       </c>
@@ -10561,8 +11249,12 @@
       <c r="R72" s="1">
         <v>73807.5</v>
       </c>
-    </row>
-    <row r="73" spans="1:18">
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73" s="10">
         <v>1994</v>
       </c>
@@ -10618,8 +11310,12 @@
       <c r="R73" s="1">
         <v>78321.700000000012</v>
       </c>
-    </row>
-    <row r="74" spans="1:18">
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74" s="10">
         <v>1995</v>
       </c>
@@ -10675,8 +11371,12 @@
       <c r="R74" s="1">
         <v>86247.4</v>
       </c>
-    </row>
-    <row r="75" spans="1:18">
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75" s="10">
         <v>1996</v>
       </c>
@@ -10732,8 +11432,12 @@
       <c r="R75" s="1">
         <v>94861.7</v>
       </c>
-    </row>
-    <row r="76" spans="1:18">
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76" s="10">
         <v>1997</v>
       </c>
@@ -10789,8 +11493,12 @@
       <c r="R76" s="1">
         <v>103295.8</v>
       </c>
-    </row>
-    <row r="77" spans="1:18">
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77" s="10">
         <v>1998</v>
       </c>
@@ -10846,8 +11554,12 @@
       <c r="R77" s="1">
         <v>111022.40000000001</v>
       </c>
-    </row>
-    <row r="78" spans="1:18">
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78" s="10">
         <v>1999</v>
       </c>
@@ -10903,8 +11615,12 @@
       <c r="R78" s="1">
         <v>116439.9</v>
       </c>
-    </row>
-    <row r="79" spans="1:18">
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79" s="10">
         <v>2000</v>
       </c>
@@ -10960,8 +11676,12 @@
       <c r="R79" s="1">
         <v>124921.59999999999</v>
       </c>
-    </row>
-    <row r="80" spans="1:18">
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79" s="3"/>
+      <c r="W79" s="3"/>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80" s="10">
         <v>2001</v>
       </c>
@@ -11017,8 +11737,12 @@
       <c r="R80" s="1">
         <v>122724.69999999998</v>
       </c>
-    </row>
-    <row r="81" spans="1:18">
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81" s="10">
         <v>2002</v>
       </c>
@@ -11074,8 +11798,12 @@
       <c r="R81" s="1">
         <v>129399.5</v>
       </c>
-    </row>
-    <row r="82" spans="1:18">
+      <c r="T81" s="3"/>
+      <c r="U81" s="3"/>
+      <c r="V81" s="3"/>
+      <c r="W81" s="3"/>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82" s="10">
         <v>2003</v>
       </c>
@@ -11131,8 +11859,12 @@
       <c r="R82" s="1">
         <v>140580.5</v>
       </c>
-    </row>
-    <row r="83" spans="1:18">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83" s="10">
         <v>2004</v>
       </c>
@@ -11188,8 +11920,12 @@
       <c r="R83" s="1">
         <v>150698.29999999999</v>
       </c>
-    </row>
-    <row r="84" spans="1:18">
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84" s="10">
         <v>2005</v>
       </c>
@@ -11245,8 +11981,12 @@
       <c r="R84" s="1">
         <v>161956.19999999998</v>
       </c>
-    </row>
-    <row r="85" spans="1:18">
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85" s="10">
         <v>2006</v>
       </c>
@@ -11302,8 +12042,12 @@
       <c r="R85" s="1">
         <v>176299.8</v>
       </c>
-    </row>
-    <row r="86" spans="1:18">
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86" s="10">
         <v>2007</v>
       </c>
@@ -11359,8 +12103,12 @@
       <c r="R86" s="1">
         <v>191558.12940900002</v>
       </c>
-    </row>
-    <row r="87" spans="1:18">
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87" s="10">
         <v>2008</v>
       </c>
@@ -11416,8 +12164,12 @@
       <c r="R87" s="1">
         <v>198418.00000000003</v>
       </c>
-    </row>
-    <row r="88" spans="1:18">
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A88" s="10">
         <v>2009</v>
       </c>
@@ -11473,8 +12225,12 @@
       <c r="R88" s="1">
         <v>194812.92600000001</v>
       </c>
-    </row>
-    <row r="89" spans="1:18">
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A89" s="10">
         <v>2010</v>
       </c>
@@ -11530,8 +12286,12 @@
       <c r="R89" s="1">
         <v>211207.7</v>
       </c>
-    </row>
-    <row r="90" spans="1:18">
+      <c r="T89" s="3"/>
+      <c r="U89" s="3"/>
+      <c r="V89" s="3"/>
+      <c r="W89" s="3"/>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90" s="10">
         <v>2011</v>
       </c>
@@ -11587,8 +12347,12 @@
       <c r="R90" s="1">
         <v>229395.10000000003</v>
       </c>
-    </row>
-    <row r="91" spans="1:18">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91" s="10">
         <v>2012</v>
       </c>
@@ -11644,8 +12408,12 @@
       <c r="R91" s="1">
         <v>239496.8</v>
       </c>
-    </row>
-    <row r="92" spans="1:18">
+      <c r="T91" s="3"/>
+      <c r="U91" s="3"/>
+      <c r="V91" s="3"/>
+      <c r="W91" s="3"/>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92" s="10">
         <v>2013</v>
       </c>
@@ -11701,8 +12469,12 @@
       <c r="R92" s="1">
         <v>240153.95300000001</v>
       </c>
-    </row>
-    <row r="93" spans="1:18">
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A93" s="10">
         <v>2014</v>
       </c>
@@ -11758,8 +12530,12 @@
       <c r="R93" s="1">
         <v>251962.81699999998</v>
       </c>
-    </row>
-    <row r="94" spans="1:18">
+      <c r="T93" s="3"/>
+      <c r="U93" s="3"/>
+      <c r="V93" s="3"/>
+      <c r="W93" s="3"/>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A94" s="10">
         <v>2015</v>
       </c>
@@ -11815,8 +12591,12 @@
       <c r="R94" s="1">
         <v>261783.30354659999</v>
       </c>
-    </row>
-    <row r="95" spans="1:18">
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A95" s="10">
         <v>2016</v>
       </c>
@@ -11873,8 +12653,12 @@
       <c r="R95" s="1">
         <v>274407.74903779023</v>
       </c>
-    </row>
-    <row r="96" spans="1:18">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A96" s="10">
         <v>2017</v>
       </c>
@@ -11931,8 +12715,12 @@
       <c r="R96" s="1">
         <v>297277.52293600002</v>
       </c>
-    </row>
-    <row r="97" spans="1:18">
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <v>2018</v>
       </c>
@@ -11989,8 +12777,12 @@
       <c r="R97" s="1">
         <v>304801.88501538563</v>
       </c>
-    </row>
-    <row r="98" spans="1:18">
+      <c r="T97" s="3"/>
+      <c r="U97" s="3"/>
+      <c r="V97" s="3"/>
+      <c r="W97" s="3"/>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98" s="10">
         <v>2019</v>
       </c>
@@ -12047,8 +12839,12 @@
       <c r="R98" s="1">
         <v>303897.55961765966</v>
       </c>
-    </row>
-    <row r="99" spans="1:18">
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99" s="10">
         <v>2020</v>
       </c>
@@ -12105,8 +12901,12 @@
       <c r="R99" s="1">
         <v>306703.09244441759</v>
       </c>
-    </row>
-    <row r="100" spans="1:18">
+      <c r="T99" s="3"/>
+      <c r="U99" s="3"/>
+      <c r="V99" s="3"/>
+      <c r="W99" s="3"/>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100" s="10">
         <v>2021</v>
       </c>
@@ -12163,8 +12963,12 @@
       <c r="R100" s="1">
         <v>334723.1119286996</v>
       </c>
-    </row>
-    <row r="101" spans="1:18">
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101" s="10">
         <v>2022</v>
       </c>
@@ -12220,8 +13024,12 @@
       <c r="R101" s="1">
         <v>328379.34151660191</v>
       </c>
-    </row>
-    <row r="102" spans="1:18">
+      <c r="T101" s="3"/>
+      <c r="U101" s="3"/>
+      <c r="V101" s="3"/>
+      <c r="W101" s="3"/>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102" s="10">
         <v>2023</v>
       </c>
@@ -12277,14 +13085,18 @@
       <c r="R102" s="1">
         <v>331148.8951393959</v>
       </c>
-    </row>
-    <row r="103" spans="1:18">
+      <c r="T102" s="3"/>
+      <c r="U102" s="3"/>
+      <c r="V102" s="3"/>
+      <c r="W102" s="3"/>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J105" s="3"/>
     </row>
   </sheetData>
